--- a/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C26" t="n">
         <v>84</v>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C35" t="n">
         <v>232</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="C37" t="n">
         <v>343</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4280</v>
+        <v>4283</v>
       </c>
       <c r="C38" t="n">
         <v>186</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7449</v>
+        <v>7450</v>
       </c>
       <c r="C40" t="n">
         <v>228</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6476</v>
+        <v>6480</v>
       </c>
       <c r="C41" t="n">
         <v>289</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5696</v>
+        <v>5698</v>
       </c>
       <c r="C42" t="n">
         <v>249</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7199</v>
+        <v>7200</v>
       </c>
       <c r="C43" t="n">
         <v>294</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7113</v>
+        <v>7128</v>
       </c>
       <c r="C44" t="n">
         <v>437</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>5486</v>
+        <v>5524</v>
       </c>
       <c r="C45" t="n">
         <v>384</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5094</v>
+        <v>5109</v>
       </c>
       <c r="C46" t="n">
         <v>436</v>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6089</v>
+        <v>6101</v>
       </c>
       <c r="C47" t="n">
         <v>540</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7022</v>
+        <v>7026</v>
       </c>
       <c r="C48" t="n">
         <v>532</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-10T11:04:53</t>
+          <t>2026-10-10T17:56:26</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>135,413</t>
+          <t>135,512</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>1,066</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.46 seconds</t>
+          <t>1.17 seconds</t>
         </is>
       </c>
     </row>

--- a/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Run info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5870</v>
+        <v>5881</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5720</v>
+        <v>5726</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4578</v>
+        <v>4580</v>
       </c>
       <c r="C19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4488</v>
+        <v>4490</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="C22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2076</v>
+        <v>2085</v>
       </c>
       <c r="C23" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1815</v>
+        <v>1825</v>
       </c>
       <c r="C25" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>1773</v>
       </c>
       <c r="C26" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1843</v>
+        <v>1874</v>
       </c>
       <c r="C27" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2438</v>
+        <v>2507</v>
       </c>
       <c r="C28" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1746</v>
+        <v>1792</v>
       </c>
       <c r="C29" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2080</v>
+        <v>2126</v>
       </c>
       <c r="C30" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1587</v>
+        <v>1672</v>
       </c>
       <c r="C31" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1408</v>
+        <v>1480</v>
       </c>
       <c r="C32" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1422</v>
+        <v>1497</v>
       </c>
       <c r="C33" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1535</v>
+        <v>1583</v>
       </c>
       <c r="C34" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35">
@@ -869,10 +869,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1374</v>
+        <v>1427</v>
       </c>
       <c r="C35" t="n">
-        <v>232</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1761</v>
+        <v>1803</v>
       </c>
       <c r="C36" t="n">
-        <v>242</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2351</v>
+        <v>2401</v>
       </c>
       <c r="C37" t="n">
-        <v>343</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4283</v>
+        <v>4241</v>
       </c>
       <c r="C38" t="n">
-        <v>186</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6405</v>
+        <v>6390</v>
       </c>
       <c r="C39" t="n">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7450</v>
+        <v>7445</v>
       </c>
       <c r="C40" t="n">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6480</v>
+        <v>6468</v>
       </c>
       <c r="C41" t="n">
-        <v>289</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5698</v>
+        <v>5693</v>
       </c>
       <c r="C42" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7200</v>
+        <v>7204</v>
       </c>
       <c r="C43" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7128</v>
+        <v>7121</v>
       </c>
       <c r="C44" t="n">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>5524</v>
       </c>
       <c r="C45" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5109</v>
+        <v>5128</v>
       </c>
       <c r="C46" t="n">
-        <v>436</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6101</v>
+        <v>6131</v>
       </c>
       <c r="C47" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
     </row>
     <row r="48">
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7026</v>
+        <v>7036</v>
       </c>
       <c r="C48" t="n">
-        <v>532</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-10T17:56:26</t>
+          <t>2026-10-15T18:46:39</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>135,512</t>
+          <t>136,150</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1,066</t>
+          <t>4,119</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.17 seconds</t>
+          <t>2.15 seconds</t>
         </is>
       </c>
     </row>

--- a/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-15T18:46:39</t>
+          <t>2026-10-15T21:48:20</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.15 seconds</t>
+          <t>1.97 seconds</t>
         </is>
       </c>
     </row>

--- a/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
+++ b/0-assets/raw_data/main/3b-age-grouping/age_young_old_quarterly_statistics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Quarterly counts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Run info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3623</v>
+        <v>3629</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5881</v>
+        <v>5889</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5726</v>
+        <v>5731</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4580</v>
+        <v>4582</v>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2671</v>
+        <v>2678</v>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C26" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C27" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C32" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33">
@@ -924,7 +924,7 @@
         <v>6390</v>
       </c>
       <c r="C39" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40">
@@ -937,7 +937,7 @@
         <v>7445</v>
       </c>
       <c r="C40" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>6468</v>
       </c>
       <c r="C41" t="n">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="42">
@@ -963,7 +963,7 @@
         <v>5693</v>
       </c>
       <c r="C42" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43">
@@ -976,7 +976,7 @@
         <v>7204</v>
       </c>
       <c r="C43" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>7121</v>
       </c>
       <c r="C44" t="n">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45">
@@ -1002,7 +1002,7 @@
         <v>5524</v>
       </c>
       <c r="C45" t="n">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>5128</v>
       </c>
       <c r="C46" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>6131</v>
       </c>
       <c r="C47" t="n">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="48">
@@ -1041,7 +1041,7 @@
         <v>7036</v>
       </c>
       <c r="C48" t="n">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-15T21:48:20</t>
+          <t>2026-10-17T22:04:48</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>136,150</t>
+          <t>136,183</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4,119</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.97 seconds</t>
+          <t>1.30 seconds</t>
         </is>
       </c>
     </row>
